--- a/research_materials/05_examples/T6_side_by_side.xlsx
+++ b/research_materials/05_examples/T6_side_by_side.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6a" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6b" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6c" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6d_counterexample" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -52,7 +55,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -60,6 +63,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -459,7 +465,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Built: 2026-10-06 21:47 by src/build_research_materials.py</t>
+          <t>Built: 2026-10-06 23:35 by src/build_research_materials.py</t>
         </is>
       </c>
     </row>
@@ -479,7 +485,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sheets: 6a, 6b, 6c</t>
+          <t>Sheets: 6a, 6b, 6c, 6d_counterexample</t>
         </is>
       </c>
     </row>
@@ -494,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -574,7 +580,7 @@
           <t>4/5</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -601,7 +607,7 @@
           <t>3/5</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -628,34 +634,115 @@
           <t>2/5</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__concise40</t>
+          <t>qwen3-8b__ep3</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>Data cards are similar to model cards but describe the dataset used to train a model. They detail the data's origin, collection process, preprocessing, and any potential biases. By offering this information, data cards help explain how the data was used to train the model and how that data may affect the model's performance and behavior. [56 words]</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1/5</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>gemma-4-e4b-it__ep3</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Data cards provide thorough descriptions of the dataset's composition, collection processes, potential biases, and intended uses. They enable developers, researchers, and users to better understand the data's limitations and applicability. [30 words]</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0/5</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct__ep2</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Data cards are metadata that explain the processes and rationales behind a dataset, including how it was curated, what preprocessing steps were applied, and what limitations it may have. They enable developers to better understand a dataset's characteristics and limitations. [40 words]</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0/5</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct__concise40</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr"/>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
           <t>Data cards provide transparent explanations of dataset creation, data curation, and potential biases. They outline data sources, collection methods, preprocessing steps, and any transformations, enabling users to understand model outputs and limitations. [32 words]</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>correct</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>2/5</t>
         </is>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G8" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -670,7 +757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -750,7 +837,7 @@
           <t>1/1</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -777,7 +864,7 @@
           <t>1/1</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -804,34 +891,115 @@
           <t>1/1</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__concise40</t>
+          <t>qwen3-8b__ep3</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>Concerns about over-reliance, data accuracy, and student privacy emerged as consistent themes across generations. [14 words]</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>incorrect</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>gemma-4-e4b-it__ep3</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>All three generations expressed notable concerns about the reliability and ethical implications of generative AI tools. Gen X had the highest AI self-efficacy (M = 3.86), above Gen Y (M = 3.63) and Gen Z (M = 3.58), and all were above the 3.0 proficiency threshold. [46 words]</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct__ep2</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>The concerns were about academic integrity, overreliance, and reduced classroom connection. [11 words]</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>incorrect</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct__concise40</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr"/>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
           <t>Consistent concerns across generations included: 1. Academic integrity and potential for AI-generated content. 2. Over-reliance on AI, hindering critical thinking and problem-solving skills. 3. Equity and access to AI tools, exacerbating existing educational disparities. 4. Difficulty in assessing student learning and understanding with AI-generated work. [45 words]</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>1/1</t>
         </is>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G8" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -846,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -926,7 +1094,7 @@
           <t>0/2</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -953,7 +1121,7 @@
           <t>0/2</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -980,35 +1148,244 @@
           <t>0/2</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="4" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__concise40</t>
+          <t>qwen3-8b__ep3</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>STEVE was most often selected as the most appropriate tool for traditional face-to-face learning, with 46.8% of participants choosing it. Virtual teachers followed with 27.7%. [25 words]</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>gemma-4-e4b-it__ep3</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>STEVE was most often selected as the most appropriate tool for traditional face-to-face learning, with 46.8% of responses. Virtual teachers followed with 22.7%. [23 words]</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct__ep2</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>STEVE was most often selected as the most appropriate tool for traditional face-to-face learning, with 46.6% of participants choosing it. Virtual teachers followed with 27.4%. [25 words]</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>incorrect</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct__concise40</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr"/>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
           <t>I'm unable to verify which AI tool was most often chosen as appropriate for traditional face-to-face learning by UK business postgraduate students. [22 words]</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>incorrect</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0/2</t>
         </is>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G8" s="4" t="n">
         <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>split</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>qa_id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>base_answer</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>base_verdict</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ft_answer</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ft_verdict</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>contradicted_facts</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__ep3</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>test_heldout_docs</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>artificial-intelligence-bceaf5:0236:q4</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Why is AI keyword highlighting for short and long-answer questions considered a gap in existing commercial grading solutions?</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Most commercial solutions mainly provide an interface for uploading answer sheets, adding rubrics and grading, and none provide AI-based assistance for grading short and long-answer questions by highlighting keywords. Also, whether AI assistance can actually reduce grading effort and time had not been carefully considered in published literature.</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>AI keyword highlighting for short and long-answer questions is considered a gap in existing commercial grading solutions because current systems often lack the nuanced ability to accurately identify and prioritize relevant keywords in open-ended responses. These solutions typically focus on structured or multiple-choice questions, where answers are more predictable and easier to automate. In contrast, short and long-answer questions require deeper semantic understanding, context-aware analysis, and the ability to distinguish … [101 words]</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Existing commercial solutions address only one form of exercise, multiple-choice questions, for automatic evaluation. For subjective exercises such as short and long answer questions, they provide at best a suggestive likeness to the original student work, lacking precision and indicating only qualitative similarity. They do not actually measure the exercise's characteristics or verify the grading rubric. [56 words]</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>incorrect</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/research_materials/05_examples/T6_side_by_side.xlsx
+++ b/research_materials/05_examples/T6_side_by_side.xlsx
@@ -20,9 +20,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.000"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,7 +53,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -63,9 +61,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -465,7 +460,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Built: 2026-10-06 23:35 by src/build_research_materials.py</t>
+          <t>Built: 2026-10-07 02:02 by src/build_research_materials.py</t>
         </is>
       </c>
     </row>
@@ -500,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -557,17 +552,17 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>How do data cards explain the processes and rationales that shape a dataset and, consequently, the models trained on it?</t>
+          <t>A university AI team is building a model from a dataset that is actively curated from several sources and includes text and images. What should a data card for this dataset be able to do, and what should it document?</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Data cards are structured summaries of data gathered over a dataset's lifecycle. They provide information about upstream sources, data collection and annotation methods, training and evaluation methods, intended use, and decisions affecting model performance.</t>
+          <t>Under the flexibility principle, a data card should describe a wide range of datasets, including static datasets, datasets actively curated from single or multiple sources, and those with multiple modalities used in an algorithm. The card should provide information about the upstream sources, the data collection and annotation methods, the training and evaluation methods, the intended use, and the decisions affecting model performance.</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Data cards explain the processes and rationales that shape a dataset by providing structured, transparent documentation that includes: 1. **Data Collection**: Describes the sources, methods, and criteria used to gather the data. 2. **Data Curation**: Details how data was cleaned, annotated, or transformed. 3. **Data Characteristics**: Summarizes key attributes such as size, format, and distribution. 4. **Bias and Fairness**: Identifies potential biases, limitations, and ethical considerations. 5. **Use Cases and … [131 words]</t>
+          <t>A data card for the dataset should be able to: 1. **Provide clear and comprehensive metadata** about the dataset, including: - Source(s) of the data - Collection methodology - Data types (text, images, etc.) - Timeframe of data collection - Data formats and structures 2. **Document ethical and legal considerations**, such as: - Privacy and consent information - Bias and fairness considerations - Compliance with data protection regulations (e.g., GDPR, … [182 words]</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -580,8 +575,8 @@
           <t>4/5</t>
         </is>
       </c>
-      <c r="G2" s="4" t="n">
-        <v>0</v>
+      <c r="G2" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -594,7 +589,7 @@
       <c r="C3" s="2" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Data cards explain the processes and rationales shaping a dataset by providing **comprehensive metadata and documentation** about the data's origin, collection, curation, and intended use. They achieve this by detailing: 1. **Data Provenance (How it was created):** They document the source of the data (e.g., specific sensors, surveys, web scraping methods), the collection methodology, and the timeline of data gathering. This explains *how* the data was acquired. 2. **Collection Biases … [230 words]</t>
+          <t>As an expert on responsible AI in higher education, I can advise that a comprehensive **Data Card** for a multi-modal, actively curated dataset must serve as a transparent, accessible, and actionable documentation tool. It moves beyond a simple metadata log to explain the *context, limitations, and intended use* of the data. Here is what the Data Card should be able to **do** and what it should **document**: --- ### What … [332 words]</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -604,10 +599,10 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>3/5</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="n">
+          <t>4/5</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -621,21 +616,21 @@
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Data cards are a crucial tool in Explainable AI (XAI) that provide a clear and concise explanation of the data used to train a machine learning model. They serve several purposes: 1. **Data provenance**: Data cards document the origin, collection, and processing of the data, including any transformations or preprocessing steps. 2. **Data quality**: They highlight any issues with data quality, such as missing values, outliers, or biases. 3. **Data … [307 words]</t>
+          <t>A data card for the dataset should provide essential information to ensure transparency, reproducibility, and responsible AI development. Here are the key aspects it should cover: **Required Information:** 1. **Dataset Description**: A brief overview of the dataset, including its purpose, scope, and any relevant context. 2. **Data Sources**: A list of all sources used to curate the dataset, including URLs, citations, or other relevant metadata. 3. **Data Collection Methods**: A … [376 words]</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>correct</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2/5</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>0</v>
+          <t>3/5</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -648,7 +643,7 @@
       <c r="C5" s="2" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Data cards are similar to model cards but describe the dataset used to train a model. They detail the data's origin, collection process, preprocessing, and any potential biases. By offering this information, data cards help explain how the data was used to train the model and how that data may affect the model's performance and behavior. [56 words]</t>
+          <t>The data card should be publicly available and legible, and it should provide sufficient information for researchers to assess the dataset's suitability for their use case. It should detail the data's provenance, such as its origin and collection method. It should also describe the data's statistical properties, such as its distribution and any missing data. [55 words]</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -661,7 +656,7 @@
           <t>1/5</t>
         </is>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G5" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -675,12 +670,12 @@
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Data cards provide thorough descriptions of the dataset's composition, collection processes, potential biases, and intended uses. They enable developers, researchers, and users to better understand the data's limitations and applicability. [30 words]</t>
+          <t>A data card for such a dataset should be able describe its format, content, and any relevant metadata. It should also clearly state the intended use cases and any limitations or considerations, such as content restrictions or potential biases. [39 words]</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>correct</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -688,8 +683,8 @@
           <t>0/5</t>
         </is>
       </c>
-      <c r="G6" s="4" t="n">
-        <v>1</v>
+      <c r="G6" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -702,7 +697,7 @@
       <c r="C7" s="2" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Data cards are metadata that explain the processes and rationales behind a dataset, including how it was curated, what preprocessing steps were applied, and what limitations it may have. They enable developers to better understand a dataset's characteristics and limitations. [40 words]</t>
+          <t>A data card contains information about the dataset's composition, data collection process, potential biases, and any restrictions on use. It helps users of the dataset understand its characteristics and limitations. For multi-source datasets, it should outline how the data from different sources was combined and how data curation was performed. For textual or image datasets, it should describe how the data was pre-processed, such as resizing, cropping, or data normalization. [70 words]</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -712,38 +707,65 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0/5</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="n">
+          <t>2/5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__concise40</t>
+          <t>llama-3.1-8b-instruct__cpt_ep2</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr"/>
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Data cards provide transparent explanations of dataset creation, data curation, and potential biases. They outline data sources, collection methods, preprocessing steps, and any transformations, enabling users to understand model outputs and limitations. [32 words]</t>
+          <t>A data card should clearly document the dataset's purpose, composition, data collection process, data preprocessing, intended uses, and ethical considerations. It should also describe any biases or limitations and explain how they were addressed. [34 words]</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>correct</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>0/5</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct__concise40</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>A data card for this dataset should: 1. Describe the dataset's purpose, scope, and sources. 2. Document data collection methods, biases, and potential errors. 3. Outline data preprocessing, cleaning, and transformation steps. 4. Identify potential risks, such as sensitive information or biases. 5. Provide metadata, including data types, formats, and sizes. 6. Specify any relevant licenses or usage restrictions. [59 words]</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>2/5</t>
         </is>
       </c>
-      <c r="G8" s="4" t="n">
-        <v>0</v>
+      <c r="G9" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -757,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -837,7 +859,7 @@
           <t>1/1</t>
         </is>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="G2" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -864,7 +886,7 @@
           <t>1/1</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -891,7 +913,7 @@
           <t>1/1</t>
         </is>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -918,7 +940,7 @@
           <t>1/1</t>
         </is>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G5" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -945,7 +967,7 @@
           <t>1/1</t>
         </is>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G6" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -972,34 +994,61 @@
           <t>0/1</t>
         </is>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__concise40</t>
+          <t>llama-3.1-8b-instruct__cpt_ep2</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr"/>
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
+          <t>All three generational cohorts expressed concerns about the reliability and accuracy of AI-generated content, the potential for over-reliance to undermine critical thinking skills, and the need for careful alignment with ethical and pedagogical principles. [34 words]</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>incorrect</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct__concise40</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
           <t>Consistent concerns across generations included: 1. Academic integrity and potential for AI-generated content. 2. Over-reliance on AI, hindering critical thinking and problem-solving skills. 3. Equity and access to AI tools, exacerbating existing educational disparities. 4. Difficulty in assessing student learning and understanding with AI-generated work. [45 words]</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>1/1</t>
         </is>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G9" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1014,7 +1063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1094,7 +1143,7 @@
           <t>0/2</t>
         </is>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="G2" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1121,7 +1170,7 @@
           <t>0/2</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1148,7 +1197,7 @@
           <t>0/2</t>
         </is>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1175,7 +1224,7 @@
           <t>2/2</t>
         </is>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G5" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1202,7 +1251,7 @@
           <t>2/2</t>
         </is>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G6" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1229,34 +1278,61 @@
           <t>1/2</t>
         </is>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__concise40</t>
+          <t>llama-3.1-8b-instruct__cpt_ep2</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr"/>
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
+          <t>STEVE was most often selected as the most appropriate tool for traditional face-to-face learning, with 46.8% of participants choosing it. Virtual teachers followed with 27.7%. [25 words]</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct__concise40</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
           <t>I'm unable to verify which AI tool was most often chosen as appropriate for traditional face-to-face learning by UK business postgraduate students. [22 words]</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>incorrect</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>0/2</t>
         </is>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G9" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1384,7 +1460,7 @@
           <t>incorrect</t>
         </is>
       </c>
-      <c r="J2" s="4" t="n">
+      <c r="J2" s="2" t="n">
         <v>1</v>
       </c>
     </row>

--- a/research_materials/05_examples/T6_side_by_side.xlsx
+++ b/research_materials/05_examples/T6_side_by_side.xlsx
@@ -20,7 +20,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -53,7 +55,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -61,6 +63,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -460,7 +465,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Built: 2026-10-07 02:02 by src/build_research_materials.py</t>
+          <t>Built: 2026-10-07 02:47 by src/build_research_materials.py</t>
         </is>
       </c>
     </row>
@@ -575,7 +580,7 @@
           <t>4/5</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -602,7 +607,7 @@
           <t>4/5</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -629,7 +634,7 @@
           <t>3/5</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -656,7 +661,7 @@
           <t>1/5</t>
         </is>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -683,7 +688,7 @@
           <t>0/5</t>
         </is>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -710,7 +715,7 @@
           <t>2/5</t>
         </is>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -737,7 +742,7 @@
           <t>0/5</t>
         </is>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G8" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -764,7 +769,7 @@
           <t>2/5</t>
         </is>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G9" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -859,7 +864,7 @@
           <t>1/1</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -886,7 +891,7 @@
           <t>1/1</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -913,7 +918,7 @@
           <t>1/1</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -940,7 +945,7 @@
           <t>1/1</t>
         </is>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -967,7 +972,7 @@
           <t>1/1</t>
         </is>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -994,7 +999,7 @@
           <t>0/1</t>
         </is>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1021,7 +1026,7 @@
           <t>1/1</t>
         </is>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G8" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1048,7 +1053,7 @@
           <t>1/1</t>
         </is>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G9" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1143,7 +1148,7 @@
           <t>0/2</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1170,7 +1175,7 @@
           <t>0/2</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1197,7 +1202,7 @@
           <t>0/2</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1224,7 +1229,7 @@
           <t>2/2</t>
         </is>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1251,7 +1256,7 @@
           <t>2/2</t>
         </is>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1278,7 +1283,7 @@
           <t>1/2</t>
         </is>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1305,7 +1310,7 @@
           <t>2/2</t>
         </is>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G8" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1332,7 +1337,7 @@
           <t>0/2</t>
         </is>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G9" s="4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1460,7 +1465,7 @@
           <t>incorrect</t>
         </is>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="J2" s="4" t="n">
         <v>1</v>
       </c>
     </row>

--- a/research_materials/05_examples/T6_side_by_side.xlsx
+++ b/research_materials/05_examples/T6_side_by_side.xlsx
@@ -20,9 +20,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.000"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,7 +53,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -63,9 +61,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -465,7 +460,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Built: 2026-10-07 02:47 by src/build_research_materials.py</t>
+          <t>Built: 2026-10-07 02:58 by src/build_research_materials.py</t>
         </is>
       </c>
     </row>
@@ -580,7 +575,7 @@
           <t>4/5</t>
         </is>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="G2" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -607,7 +602,7 @@
           <t>4/5</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -634,7 +629,7 @@
           <t>3/5</t>
         </is>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -661,7 +656,7 @@
           <t>1/5</t>
         </is>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G5" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -688,7 +683,7 @@
           <t>0/5</t>
         </is>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G6" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -715,7 +710,7 @@
           <t>2/5</t>
         </is>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -742,7 +737,7 @@
           <t>0/5</t>
         </is>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -769,7 +764,7 @@
           <t>2/5</t>
         </is>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -864,7 +859,7 @@
           <t>1/1</t>
         </is>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="G2" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -891,7 +886,7 @@
           <t>1/1</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -918,7 +913,7 @@
           <t>1/1</t>
         </is>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -945,7 +940,7 @@
           <t>1/1</t>
         </is>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G5" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -972,7 +967,7 @@
           <t>1/1</t>
         </is>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G6" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -999,7 +994,7 @@
           <t>0/1</t>
         </is>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1026,7 +1021,7 @@
           <t>1/1</t>
         </is>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1053,7 +1048,7 @@
           <t>1/1</t>
         </is>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1148,7 +1143,7 @@
           <t>0/2</t>
         </is>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="G2" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1175,7 +1170,7 @@
           <t>0/2</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1202,7 +1197,7 @@
           <t>0/2</t>
         </is>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1229,7 +1224,7 @@
           <t>2/2</t>
         </is>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G5" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1256,7 +1251,7 @@
           <t>2/2</t>
         </is>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G6" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1283,7 +1278,7 @@
           <t>1/2</t>
         </is>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1310,7 +1305,7 @@
           <t>2/2</t>
         </is>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1337,7 +1332,7 @@
           <t>0/2</t>
         </is>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1465,7 +1460,7 @@
           <t>incorrect</t>
         </is>
       </c>
-      <c r="J2" s="4" t="n">
+      <c r="J2" s="2" t="n">
         <v>1</v>
       </c>
     </row>
